--- a/output/pdf_financials_xlsx/PZA.xlsx
+++ b/output/pdf_financials_xlsx/PZA.xlsx
@@ -1025,16 +1025,16 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="13">
@@ -2360,25 +2360,25 @@
         <v>2.122</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.535</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.657</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.936</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.505</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="35">
@@ -2458,25 +2458,25 @@
         <v>4.872</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.75</v>
+        <v>3.91</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.75</v>
+        <v>3.285</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>3.5</v>
+        <v>6.157</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>6</v>
+        <v>7.936</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6</v>
+        <v>8.505000000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>5</v>
+        <v>5.781</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>3</v>
+        <v>3.584</v>
       </c>
     </row>
     <row r="37">
@@ -3046,25 +3046,25 @@
         <v>3.288</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.316</v>
+        <v>3.156</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.839</v>
+        <v>3.304</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.78</v>
+        <v>3.123</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.299</v>
+        <v>3.363</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>6.194</v>
+        <v>3.689</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.488</v>
+        <v>3.707</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.19</v>
+        <v>3.606</v>
       </c>
     </row>
     <row r="49">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">

--- a/output/pdf_financials_xlsx/PZA.xlsx
+++ b/output/pdf_financials_xlsx/PZA.xlsx
@@ -6359,7 +6359,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -12872,7 +12872,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -15058,7 +15062,11 @@
           <t>Deferred tax expense (note 7)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -16142,7 +16150,11 @@
           <t>Proceeds on short-term investments</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -16738,7 +16750,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -17162,7 +17178,11 @@
           <t>Deferred income tax expense (note 8)</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E123" s="5" t="n">
         <v>2.878</v>
       </c>
